--- a/inputs/data_symbols_TD/15_LTAN06_800km_1213COLD_MY_STTLCT_HEAT_MY_0p5.xlsx
+++ b/inputs/data_symbols_TD/15_LTAN06_800km_1213COLD_MY_STTLCT_HEAT_MY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8F58473-CDAF-4289-BE99-E394C06D2705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FC2789E-85E6-401E-84DB-E47F6B1EDDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{8E9A007C-BA9E-4075-B810-BFBC26186F4F}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{77F509BC-0553-4762-BE98-0769C680B515}"/>
   </bookViews>
   <sheets>
     <sheet name="15_LTAN06_800km_1213COLD_MY_STT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F11B8A18-16E0-484D-B30F-805025E5BDEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6E185DF-36E4-4D04-AD44-AF00CBF34EE3}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>92.176240000000007</v>
+        <v>80.720160000000007</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>92.176240000000007</v>
+        <v>80.720160000000007</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>92.17653</v>
+        <v>80.720150000000004</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>92.177589999999995</v>
+        <v>80.720269999999999</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>92.179739999999995</v>
+        <v>80.720709999999997</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>92.183179999999993</v>
+        <v>80.721630000000005</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>92.188090000000003</v>
+        <v>80.723159999999993</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>92.194630000000004</v>
+        <v>80.725390000000004</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>92.202950000000001</v>
+        <v>80.728430000000003</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>92.213179999999994</v>
+        <v>80.732370000000003</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>92.225430000000003</v>
+        <v>80.737290000000002</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>92.239800000000002</v>
+        <v>80.743260000000006</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>92.256360000000001</v>
+        <v>80.750330000000005</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>92.27516</v>
+        <v>80.758529999999993</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>92.296229999999994</v>
+        <v>80.767920000000004</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>92.319569999999999</v>
+        <v>80.778490000000005</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>92.345169999999996</v>
+        <v>80.790270000000007</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>92.372990000000001</v>
+        <v>80.803259999999995</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>92.402990000000003</v>
+        <v>80.817440000000005</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
@@ -1297,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="D21">
-        <v>92.43141</v>
+        <v>80.831059999999994</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
@@ -1311,7 +1311,7 @@
         <v>3</v>
       </c>
       <c r="D22">
-        <v>92.453829999999996</v>
+        <v>80.842039999999997</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
@@ -1325,7 +1325,7 @@
         <v>3</v>
       </c>
       <c r="D23">
-        <v>92.469359999999995</v>
+        <v>80.849890000000002</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
@@ -1339,7 +1339,7 @@
         <v>3</v>
       </c>
       <c r="D24">
-        <v>92.477289999999996</v>
+        <v>80.854200000000006</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
@@ -1353,7 +1353,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>92.476939999999999</v>
+        <v>80.854579999999999</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="D26">
-        <v>92.467669999999998</v>
+        <v>80.850620000000006</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
@@ -1381,7 +1381,7 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>92.448849999999993</v>
+        <v>80.841939999999994</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
@@ -1395,7 +1395,7 @@
         <v>3</v>
       </c>
       <c r="D28">
-        <v>92.419920000000005</v>
+        <v>80.82817</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
@@ -1409,7 +1409,7 @@
         <v>3</v>
       </c>
       <c r="D29">
-        <v>92.380409999999998</v>
+        <v>80.808970000000002</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
@@ -1423,7 +1423,7 @@
         <v>3</v>
       </c>
       <c r="D30">
-        <v>92.329920000000001</v>
+        <v>80.784080000000003</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
@@ -1437,7 +1437,7 @@
         <v>3</v>
       </c>
       <c r="D31">
-        <v>92.268209999999996</v>
+        <v>80.753280000000004</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
@@ -1451,7 +1451,7 @@
         <v>3</v>
       </c>
       <c r="D32">
-        <v>92.195149999999998</v>
+        <v>80.716419999999999</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
@@ -1465,7 +1465,7 @@
         <v>3</v>
       </c>
       <c r="D33">
-        <v>92.110709999999997</v>
+        <v>80.673410000000004</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
@@ -1479,7 +1479,7 @@
         <v>3</v>
       </c>
       <c r="D34">
-        <v>92.014970000000005</v>
+        <v>80.624229999999997</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
@@ -1493,7 +1493,7 @@
         <v>3</v>
       </c>
       <c r="D35">
-        <v>91.908109999999994</v>
+        <v>80.568889999999996</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
@@ -1507,7 +1507,7 @@
         <v>3</v>
       </c>
       <c r="D36">
-        <v>91.790369999999996</v>
+        <v>80.507469999999998</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
@@ -1521,7 +1521,7 @@
         <v>3</v>
       </c>
       <c r="D37">
-        <v>91.66207</v>
+        <v>80.440070000000006</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>91.526660000000007</v>
+        <v>80.368399999999994</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>91.388030000000001</v>
+        <v>80.294439999999994</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>91.247559999999993</v>
+        <v>80.218829999999997</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>91.106470000000002</v>
+        <v>80.142200000000003</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>90.965980000000002</v>
+        <v>80.06514</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.4">
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>90.827259999999995</v>
+        <v>79.988259999999997</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>90.691469999999995</v>
+        <v>79.912189999999995</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>90.559709999999995</v>
+        <v>79.837509999999995</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>90.432950000000005</v>
+        <v>79.764769999999999</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.4">
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>90.312039999999996</v>
+        <v>79.694460000000007</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.4">
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>90.197699999999998</v>
+        <v>79.626990000000006</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.4">
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>90.090490000000003</v>
+        <v>79.562719999999999</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.4">
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>89.990819999999999</v>
+        <v>79.501930000000002</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.4">
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>89.898979999999995</v>
+        <v>79.444820000000007</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.4">
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>89.81514</v>
+        <v>79.391570000000002</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>89.739369999999994</v>
+        <v>79.342259999999996</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.4">
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>89.671660000000003</v>
+        <v>79.296970000000002</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>89.611909999999995</v>
+        <v>79.255709999999993</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.4">
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>89.559989999999999</v>
+        <v>79.21848</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.4">
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>89.515709999999999</v>
+        <v>79.18526</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.4">
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>89.478880000000004</v>
+        <v>79.156009999999995</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.4">
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>89.44923</v>
+        <v>79.130679999999998</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.4">
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>89.426500000000004</v>
+        <v>79.109179999999995</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.4">
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>89.410420000000002</v>
+        <v>79.091430000000003</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.4">
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>89.400679999999994</v>
+        <v>79.077349999999996</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.4">
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>89.396979999999999</v>
+        <v>79.066820000000007</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.4">
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>89.399000000000001</v>
+        <v>79.059709999999995</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.4">
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>89.406419999999997</v>
+        <v>79.055899999999994</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.4">
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>89.418940000000006</v>
+        <v>79.055250000000001</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.4">
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>89.436239999999998</v>
+        <v>79.05762</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.4">
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>89.457999999999998</v>
+        <v>79.062860000000001</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>89.483909999999995</v>
+        <v>79.070809999999994</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.4">
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>89.513660000000002</v>
+        <v>79.081320000000005</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.4">
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>89.546959999999999</v>
+        <v>79.094229999999996</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.4">
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>89.583539999999999</v>
+        <v>79.109409999999997</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.4">
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>89.623130000000003</v>
+        <v>79.126720000000006</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.4">
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>89.665469999999999</v>
+        <v>79.145979999999994</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.4">
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>89.710290000000001</v>
+        <v>79.167029999999997</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.4">
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>89.757360000000006</v>
+        <v>79.189719999999994</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.4">
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>89.806420000000003</v>
+        <v>79.213899999999995</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.4">
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>89.857249999999993</v>
+        <v>79.239419999999996</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.4">
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>89.909649999999999</v>
+        <v>79.266159999999999</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.4">
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>89.963409999999996</v>
+        <v>79.293959999999998</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.4">
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>90.018370000000004</v>
+        <v>79.322710000000001</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.4">
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>90.074349999999995</v>
+        <v>79.352270000000004</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.4">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>90.131190000000004</v>
+        <v>79.382549999999995</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.4">
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>90.188749999999999</v>
+        <v>79.413430000000005</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>90.246889999999993</v>
+        <v>79.444810000000004</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.4">
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>90.305480000000003</v>
+        <v>79.476609999999994</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.4">
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>90.364419999999996</v>
+        <v>79.508740000000003</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.4">
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>90.423609999999996</v>
+        <v>79.541129999999995</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.4">
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>90.482960000000006</v>
+        <v>79.573719999999994</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.4">
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>90.542400000000001</v>
+        <v>79.606440000000006</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>90.601870000000005</v>
+        <v>79.639240000000001</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.4">
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>90.661320000000003</v>
+        <v>79.672070000000005</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.4">
@@ -2305,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>90.72072</v>
+        <v>79.704899999999995</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.4">
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>90.780010000000004</v>
+        <v>79.737690000000001</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.4">
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>90.839179999999999</v>
+        <v>79.770430000000005</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.4">
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>90.898210000000006</v>
+        <v>79.803089999999997</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.4">
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>90.957080000000005</v>
+        <v>79.835669999999993</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.4">
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>91.015799999999999</v>
+        <v>79.868139999999997</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.4">
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>91.074349999999995</v>
+        <v>79.900499999999994</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.4">
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>91.132760000000005</v>
+        <v>79.932770000000005</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.4">
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>91.191019999999995</v>
+        <v>79.964960000000005</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.4">
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>91.249170000000007</v>
+        <v>79.997069999999994</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.4">
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>91.307220000000001</v>
+        <v>80.029150000000001</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.4">
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>91.365219999999994</v>
+        <v>80.061210000000003</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.4">
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>91.423180000000002</v>
+        <v>80.093260000000001</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.4">
@@ -2487,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>91.481129999999993</v>
+        <v>80.125339999999994</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.4">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>91.539090000000002</v>
+        <v>80.157449999999997</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.4">
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>91.597089999999994</v>
+        <v>80.189629999999994</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.4">
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>91.655150000000006</v>
+        <v>80.221879999999999</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.4">
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>91.713290000000001</v>
+        <v>80.254230000000007</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.4">
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>91.771519999999995</v>
+        <v>80.286689999999993</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.4">
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>91.82987</v>
+        <v>80.319270000000003</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.4">
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>91.888350000000003</v>
+        <v>80.351990000000001</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.4">
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>91.947000000000003</v>
+        <v>80.384860000000003</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.4">
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>92.005830000000003</v>
+        <v>80.41789</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.4">
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>92.064859999999996</v>
+        <v>80.451080000000005</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.4">
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>92.124099999999999</v>
+        <v>80.484449999999995</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.4">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>92.183570000000003</v>
+        <v>80.518010000000004</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.4">
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>92.243260000000006</v>
+        <v>80.551749999999998</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.4">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>92.303200000000004</v>
+        <v>80.58569</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.4">
@@ -2697,7 +2697,7 @@
         <v>3</v>
       </c>
       <c r="D121">
-        <v>92.359589999999997</v>
+        <v>80.618070000000003</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.4">
@@ -2711,7 +2711,7 @@
         <v>3</v>
       </c>
       <c r="D122">
-        <v>92.40813</v>
+        <v>80.646820000000005</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.4">
@@ -2725,7 +2725,7 @@
         <v>3</v>
       </c>
       <c r="D123">
-        <v>92.447959999999995</v>
+        <v>80.671480000000003</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.4">
@@ -2739,7 +2739,7 @@
         <v>3</v>
       </c>
       <c r="D124">
-        <v>92.478449999999995</v>
+        <v>80.691670000000002</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.4">
@@ -2753,7 +2753,7 @@
         <v>3</v>
       </c>
       <c r="D125">
-        <v>92.499020000000002</v>
+        <v>80.707030000000003</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.4">
@@ -2767,7 +2767,7 @@
         <v>3</v>
       </c>
       <c r="D126">
-        <v>92.509119999999996</v>
+        <v>80.717200000000005</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.4">
@@ -2781,7 +2781,7 @@
         <v>3</v>
       </c>
       <c r="D127">
-        <v>92.508200000000002</v>
+        <v>80.721819999999994</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.4">
@@ -2795,7 +2795,7 @@
         <v>3</v>
       </c>
       <c r="D128">
-        <v>92.49579</v>
+        <v>80.720550000000003</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.4">
@@ -2809,7 +2809,7 @@
         <v>3</v>
       </c>
       <c r="D129">
-        <v>92.471500000000006</v>
+        <v>80.713120000000004</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.4">
@@ -2823,7 +2823,7 @@
         <v>3</v>
       </c>
       <c r="D130">
-        <v>92.435019999999994</v>
+        <v>80.699280000000002</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.4">
@@ -2837,7 +2837,7 @@
         <v>3</v>
       </c>
       <c r="D131">
-        <v>92.386200000000002</v>
+        <v>80.678849999999997</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.4">
@@ -2851,7 +2851,7 @@
         <v>3</v>
       </c>
       <c r="D132">
-        <v>92.324969999999993</v>
+        <v>80.651730000000001</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.4">
@@ -2865,7 +2865,7 @@
         <v>3</v>
       </c>
       <c r="D133">
-        <v>92.251379999999997</v>
+        <v>80.617850000000004</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.4">
@@ -2879,7 +2879,7 @@
         <v>3</v>
       </c>
       <c r="D134">
-        <v>92.165580000000006</v>
+        <v>80.577219999999997</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.4">
@@ -2893,7 +2893,7 @@
         <v>3</v>
       </c>
       <c r="D135">
-        <v>92.067809999999994</v>
+        <v>80.529899999999998</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.4">
@@ -2907,7 +2907,7 @@
         <v>3</v>
       </c>
       <c r="D136">
-        <v>91.958380000000005</v>
+        <v>80.475989999999996</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.4">
@@ -2921,7 +2921,7 @@
         <v>3</v>
       </c>
       <c r="D137">
-        <v>91.837670000000003</v>
+        <v>80.415629999999993</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.4">
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="D138">
-        <v>91.709190000000007</v>
+        <v>80.350549999999998</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.4">
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="D139">
-        <v>91.576899999999995</v>
+        <v>80.282759999999996</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.4">
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>91.442229999999995</v>
+        <v>80.212950000000006</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.4">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D141">
-        <v>91.306449999999998</v>
+        <v>80.141739999999999</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.4">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="D142">
-        <v>91.1708</v>
+        <v>80.069770000000005</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.4">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>91.036500000000004</v>
+        <v>79.997659999999996</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.4">
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="D144">
-        <v>90.904740000000004</v>
+        <v>79.926060000000007</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.4">
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="D145">
-        <v>90.77664</v>
+        <v>79.85557</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.4">
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="D146">
-        <v>90.653199999999998</v>
+        <v>79.786749999999998</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.4">
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="D147">
-        <v>90.535309999999996</v>
+        <v>79.720110000000005</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.4">
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="D148">
-        <v>90.423689999999993</v>
+        <v>79.656080000000003</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.4">
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>90.318920000000006</v>
+        <v>79.595020000000005</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.4">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>90.221450000000004</v>
+        <v>79.537239999999997</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.4">
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>90.131569999999996</v>
+        <v>79.482950000000002</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.4">
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>90.049480000000003</v>
+        <v>79.432320000000004</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.4">
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="D153">
-        <v>89.975250000000003</v>
+        <v>79.385480000000001</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.4">
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="D154">
-        <v>89.908879999999996</v>
+        <v>79.342479999999995</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.4">
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="D155">
-        <v>89.850300000000004</v>
+        <v>79.303359999999998</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.4">
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>89.799379999999999</v>
+        <v>79.268129999999999</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.4">
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="D157">
-        <v>89.755949999999999</v>
+        <v>79.236770000000007</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.4">
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="D158">
-        <v>89.719809999999995</v>
+        <v>79.209249999999997</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.4">
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="D159">
-        <v>89.690719999999999</v>
+        <v>79.185519999999997</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.4">
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="D160">
-        <v>89.668430000000001</v>
+        <v>79.165520000000001</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.4">
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="D161">
-        <v>89.652670000000001</v>
+        <v>79.149169999999998</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.4">
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>89.643129999999999</v>
+        <v>79.136369999999999</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.4">
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="D163">
-        <v>89.639529999999993</v>
+        <v>79.127030000000005</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.4">
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="D164">
-        <v>89.641559999999998</v>
+        <v>79.121030000000005</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.4">
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="D165">
-        <v>89.648899999999998</v>
+        <v>79.11824</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.4">
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="D166">
-        <v>89.661259999999999</v>
+        <v>79.118530000000007</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.4">
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="D167">
-        <v>89.678309999999996</v>
+        <v>79.121769999999998</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.4">
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="D168">
-        <v>89.699759999999998</v>
+        <v>79.127809999999997</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.4">
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="D169">
-        <v>89.725279999999998</v>
+        <v>79.136489999999995</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.4">
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="D170">
-        <v>89.754589999999993</v>
+        <v>79.147670000000005</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.4">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="D171">
-        <v>89.787390000000002</v>
+        <v>79.161199999999994</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.4">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="D172">
-        <v>89.823419999999999</v>
+        <v>79.176929999999999</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.4">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="D173">
-        <v>89.862399999999994</v>
+        <v>79.194739999999996</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.4">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="D174">
-        <v>89.904089999999997</v>
+        <v>79.214460000000003</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.4">
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="D175">
-        <v>89.948229999999995</v>
+        <v>79.235929999999996</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.4">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="D176">
-        <v>89.994569999999996</v>
+        <v>79.258989999999997</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.4">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>90.042879999999997</v>
+        <v>79.28349</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.4">
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>90.092910000000003</v>
+        <v>79.309309999999996</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.4">
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="D179">
-        <v>90.144480000000001</v>
+        <v>79.336309999999997</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.4">
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="D180">
-        <v>90.197400000000002</v>
+        <v>79.364339999999999</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.4">
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="D181">
-        <v>90.251480000000001</v>
+        <v>79.393270000000001</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.4">
@@ -3551,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="D182">
-        <v>90.306569999999994</v>
+        <v>79.423010000000005</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.4">
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="D183">
-        <v>90.362489999999994</v>
+        <v>79.453419999999994</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.4">
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="D184">
-        <v>90.419110000000003</v>
+        <v>79.484409999999997</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.4">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="D185">
-        <v>90.476299999999995</v>
+        <v>79.515889999999999</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.4">
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="D186">
-        <v>90.533929999999998</v>
+        <v>79.547749999999994</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.4">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="D187">
-        <v>90.591890000000006</v>
+        <v>79.579920000000001</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.4">
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="D188">
-        <v>90.650090000000006</v>
+        <v>79.612340000000003</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.4">
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="D189">
-        <v>90.708439999999996</v>
+        <v>79.644930000000002</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.4">
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="D190">
-        <v>90.766869999999997</v>
+        <v>79.67765</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.4">
@@ -3677,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="D191">
-        <v>90.825320000000005</v>
+        <v>79.710419999999999</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.4">
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="D192">
-        <v>90.883750000000006</v>
+        <v>79.743210000000005</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.4">
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="D193">
-        <v>90.94211</v>
+        <v>79.775989999999993</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.4">
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="D194">
-        <v>91.000370000000004</v>
+        <v>79.808710000000005</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.4">
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="D195">
-        <v>91.058499999999995</v>
+        <v>79.841369999999998</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.4">
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="D196">
-        <v>91.116479999999996</v>
+        <v>79.873940000000005</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.4">
@@ -3761,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="D197">
-        <v>91.174310000000006</v>
+        <v>79.906419999999997</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.4">
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="D198">
-        <v>91.231979999999993</v>
+        <v>79.938770000000005</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.4">
@@ -3789,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>91.289479999999998</v>
+        <v>79.971019999999996</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.4">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="D200">
-        <v>91.34684</v>
+        <v>80.003159999999994</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.4">
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="D201">
-        <v>91.404049999999998</v>
+        <v>80.035210000000006</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.4">
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="D202">
-        <v>91.46114</v>
+        <v>80.067179999999993</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.4">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="D203">
-        <v>91.518150000000006</v>
+        <v>80.099109999999996</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.4">
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="D204">
-        <v>91.575100000000006</v>
+        <v>80.131</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.4">
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="D205">
-        <v>91.632009999999994</v>
+        <v>80.162890000000004</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.4">
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="D206">
-        <v>91.688910000000007</v>
+        <v>80.194800000000001</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.4">
@@ -3901,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="D207">
-        <v>91.745829999999998</v>
+        <v>80.226740000000007</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.4">
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="D208">
-        <v>91.802790000000002</v>
+        <v>80.258740000000003</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.4">
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="D209">
-        <v>91.859809999999996</v>
+        <v>80.290809999999993</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.4">
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="D210">
-        <v>91.916910000000001</v>
+        <v>80.322969999999998</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.4">
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="D211">
-        <v>91.974100000000007</v>
+        <v>80.355230000000006</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.4">
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="D212">
-        <v>92.031419999999997</v>
+        <v>80.387619999999998</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.4">
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="D213">
-        <v>92.088880000000003</v>
+        <v>80.420140000000004</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.4">
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="D214">
-        <v>92.146510000000006</v>
+        <v>80.452809999999999</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.4">
@@ -4013,7 +4013,7 @@
         <v>0</v>
       </c>
       <c r="D215">
-        <v>92.204319999999996</v>
+        <v>80.48563</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.4">
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="D216">
-        <v>92.262330000000006</v>
+        <v>80.518619999999999</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.4">
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>92.32056</v>
+        <v>80.551779999999994</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.4">
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="D218">
-        <v>92.379019999999997</v>
+        <v>80.585130000000007</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.4">
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="D219">
-        <v>92.437709999999996</v>
+        <v>80.618660000000006</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.4">
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="D220">
-        <v>92.496639999999999</v>
+        <v>80.652389999999997</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.4">
@@ -4097,7 +4097,7 @@
         <v>3</v>
       </c>
       <c r="D221">
-        <v>92.552030000000002</v>
+        <v>80.684550000000002</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.4">
@@ -4111,7 +4111,7 @@
         <v>3</v>
       </c>
       <c r="D222">
-        <v>92.59957</v>
+        <v>80.713080000000005</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.4">
@@ -4125,7 +4125,7 @@
         <v>3</v>
       </c>
       <c r="D223">
-        <v>92.638400000000004</v>
+        <v>80.73751</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.4">
@@ -4139,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="D224">
-        <v>92.667869999999994</v>
+        <v>80.757480000000001</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.4">
@@ -4153,7 +4153,7 @@
         <v>3</v>
       </c>
       <c r="D225">
-        <v>92.687430000000006</v>
+        <v>80.77261</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.4">
@@ -4167,7 +4167,7 @@
         <v>3</v>
       </c>
       <c r="D226">
-        <v>92.6965</v>
+        <v>80.782539999999997</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.4">
@@ -4181,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="D227">
-        <v>92.694559999999996</v>
+        <v>80.786919999999995</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.4">
@@ -4195,7 +4195,7 @@
         <v>3</v>
       </c>
       <c r="D228">
-        <v>92.681129999999996</v>
+        <v>80.785420000000002</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.4">
@@ -4209,7 +4209,7 @@
         <v>3</v>
       </c>
       <c r="D229">
-        <v>92.655810000000002</v>
+        <v>80.777749999999997</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.4">
@@ -4223,7 +4223,7 @@
         <v>3</v>
       </c>
       <c r="D230">
-        <v>92.618309999999994</v>
+        <v>80.763660000000002</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.4">
@@ -4237,7 +4237,7 @@
         <v>3</v>
       </c>
       <c r="D231">
-        <v>92.568460000000002</v>
+        <v>80.742990000000006</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.4">
@@ -4251,7 +4251,7 @@
         <v>3</v>
       </c>
       <c r="D232">
-        <v>92.506209999999996</v>
+        <v>80.715620000000001</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.4">
@@ -4265,7 +4265,7 @@
         <v>3</v>
       </c>
       <c r="D233">
-        <v>92.431600000000003</v>
+        <v>80.681489999999997</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.4">
@@ -4279,7 +4279,7 @@
         <v>3</v>
       </c>
       <c r="D234">
-        <v>92.34478</v>
+        <v>80.640619999999998</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.4">
@@ -4293,7 +4293,7 @@
         <v>3</v>
       </c>
       <c r="D235">
-        <v>92.245999999999995</v>
+        <v>80.593050000000005</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.4">
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="D236">
-        <v>92.135570000000001</v>
+        <v>80.538889999999995</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.4">
@@ -4321,7 +4321,7 @@
         <v>3</v>
       </c>
       <c r="D237">
-        <v>92.013850000000005</v>
+        <v>80.478279999999998</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.4">
@@ -4335,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="D238">
-        <v>91.884379999999993</v>
+        <v>80.412959999999998</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.4">
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="D239">
-        <v>91.75112</v>
+        <v>80.344920000000002</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.4">
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="D240">
-        <v>91.615489999999994</v>
+        <v>80.274870000000007</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.4">
@@ -4377,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="D241">
-        <v>91.478769999999997</v>
+        <v>80.203419999999994</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.4">
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="D242">
-        <v>91.342190000000002</v>
+        <v>80.131200000000007</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.4">
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="D243">
-        <v>91.206980000000001</v>
+        <v>80.058859999999996</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.4">
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="D244">
-        <v>91.074330000000003</v>
+        <v>79.987030000000004</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.4">
@@ -4433,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="D245">
-        <v>90.945340000000002</v>
+        <v>79.916309999999996</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.4">
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="D246">
-        <v>90.82105</v>
+        <v>79.847260000000006</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.4">
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="D247">
-        <v>90.702299999999994</v>
+        <v>79.780389999999997</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.4">
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="D248">
-        <v>90.589849999999998</v>
+        <v>79.716139999999996</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.4">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="D249">
-        <v>90.484260000000006</v>
+        <v>79.654859999999999</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.4">
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="D250">
-        <v>90.385980000000004</v>
+        <v>79.596860000000007</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.4">
@@ -4517,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="D251">
-        <v>90.295299999999997</v>
+        <v>79.542360000000002</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.4">
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="D252">
-        <v>90.212419999999995</v>
+        <v>79.491519999999994</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.4">
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="D253">
-        <v>90.137410000000003</v>
+        <v>79.444460000000007</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.4">
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="D254">
-        <v>90.070269999999994</v>
+        <v>79.401250000000005</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.4">
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="D255">
-        <v>90.010919999999999</v>
+        <v>79.361919999999998</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.4">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="D256">
-        <v>89.959239999999994</v>
+        <v>79.326480000000004</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.4">
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="D257">
-        <v>89.915059999999997</v>
+        <v>79.294910000000002</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.4">
@@ -4615,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="D258">
-        <v>89.878169999999997</v>
+        <v>79.267189999999999</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.4">
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="D259">
-        <v>89.848349999999996</v>
+        <v>79.243260000000006</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.4">
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="D260">
-        <v>89.825320000000005</v>
+        <v>79.223060000000004</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.4">
@@ -4657,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="D261">
-        <v>89.808819999999997</v>
+        <v>79.206500000000005</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.4">
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="D262">
-        <v>89.798559999999995</v>
+        <v>79.193510000000003</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.4">
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="D263">
-        <v>89.794229999999999</v>
+        <v>79.183970000000002</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.4">
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="D264">
-        <v>89.795529999999999</v>
+        <v>79.177769999999995</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.4">
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="D265">
-        <v>89.802149999999997</v>
+        <v>79.174779999999998</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.4">
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="D266">
-        <v>89.813789999999997</v>
+        <v>79.174869999999999</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.4">
@@ -4741,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="D267">
-        <v>89.830129999999997</v>
+        <v>79.177909999999997</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.4">
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="D268">
-        <v>89.850859999999997</v>
+        <v>79.183760000000007</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.4">
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="D269">
-        <v>89.87567</v>
+        <v>79.192239999999998</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.4">
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="D270">
-        <v>89.904259999999994</v>
+        <v>79.203220000000002</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.4">
@@ -4797,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="D271">
-        <v>89.936350000000004</v>
+        <v>79.216549999999998</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.4">
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="D272">
-        <v>89.971670000000003</v>
+        <v>79.232089999999999</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.4">
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="D273">
-        <v>90.009950000000003</v>
+        <v>79.249709999999993</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.4">
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="D274">
-        <v>90.050939999999997</v>
+        <v>79.269229999999993</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.4">
@@ -4853,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="D275">
-        <v>90.094369999999998</v>
+        <v>79.290499999999994</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.4">
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="D276">
-        <v>90.140010000000004</v>
+        <v>79.313370000000006</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.4">
@@ -4881,7 +4881,7 @@
         <v>0</v>
       </c>
       <c r="D277">
-        <v>90.187610000000006</v>
+        <v>79.337680000000006</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.4">
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="D278">
-        <v>90.236940000000004</v>
+        <v>79.363299999999995</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.4">
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="D279">
-        <v>90.287819999999996</v>
+        <v>79.390100000000004</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.4">
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="D280">
-        <v>90.340040000000002</v>
+        <v>79.417940000000002</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.4">
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="D281">
-        <v>90.393420000000006</v>
+        <v>79.446680000000001</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.4">
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="D282">
-        <v>90.447810000000004</v>
+        <v>79.476219999999998</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.4">
@@ -4965,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="D283">
-        <v>90.503050000000002</v>
+        <v>79.506439999999998</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.4">
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="D284">
-        <v>90.558980000000005</v>
+        <v>79.537239999999997</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.4">
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="D285">
-        <v>90.615480000000005</v>
+        <v>79.568529999999996</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.4">
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="D286">
-        <v>90.672420000000002</v>
+        <v>79.600200000000001</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.4">
@@ -5021,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="D287">
-        <v>90.729690000000005</v>
+        <v>79.632180000000005</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.4">
@@ -5035,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="D288">
-        <v>90.787210000000002</v>
+        <v>79.664400000000001</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.4">
@@ -5049,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="D289">
-        <v>90.84487</v>
+        <v>79.696809999999999</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.4">
@@ -5063,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="D290">
-        <v>90.902619999999999</v>
+        <v>79.729330000000004</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.4">
@@ -5077,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="D291">
-        <v>90.960400000000007</v>
+        <v>79.76191</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.4">
@@ -5091,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="D292">
-        <v>91.018150000000006</v>
+        <v>79.794510000000002</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.4">
@@ -5105,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="D293">
-        <v>91.075839999999999</v>
+        <v>79.827100000000002</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.4">
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="D294">
-        <v>91.133430000000004</v>
+        <v>79.859629999999996</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.4">
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="D295">
-        <v>91.190889999999996</v>
+        <v>79.892099999999999</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.4">
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="D296">
-        <v>91.24821</v>
+        <v>79.924490000000006</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.4">
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="D297">
-        <v>91.305369999999996</v>
+        <v>79.956770000000006</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.4">
@@ -5175,7 +5175,7 @@
         <v>0</v>
       </c>
       <c r="D298">
-        <v>91.362380000000002</v>
+        <v>79.988939999999999</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.4">
@@ -5189,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="D299">
-        <v>91.419219999999996</v>
+        <v>80.021000000000001</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.4">
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="D300">
-        <v>91.475920000000002</v>
+        <v>80.052949999999996</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.4">
@@ -5217,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="D301">
-        <v>91.532480000000007</v>
+        <v>80.084810000000004</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.4">
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="D302">
-        <v>91.588920000000002</v>
+        <v>80.116590000000002</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.4">
@@ -5245,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="D303">
-        <v>91.64528</v>
+        <v>80.148330000000001</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/data_symbols_TD/15_LTAN06_800km_1213COLD_MY_STTLCT_HEAT_MY_0p5.xlsx
+++ b/inputs/data_symbols_TD/15_LTAN06_800km_1213COLD_MY_STTLCT_HEAT_MY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FC2789E-85E6-401E-84DB-E47F6B1EDDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72344886-6A95-48E0-854C-32C5ECA23FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{77F509BC-0553-4762-BE98-0769C680B515}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{8D8F8A1B-0F64-4D3F-85D3-811D3ECC1CA8}"/>
   </bookViews>
   <sheets>
     <sheet name="15_LTAN06_800km_1213COLD_MY_STT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6E185DF-36E4-4D04-AD44-AF00CBF34EE3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C6FC404-6231-4306-A719-A70924C7B8DC}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/inputs/data_symbols_TD/15_LTAN06_800km_1213COLD_MY_STTLCT_HEAT_MY_0p5.xlsx
+++ b/inputs/data_symbols_TD/15_LTAN06_800km_1213COLD_MY_STTLCT_HEAT_MY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72344886-6A95-48E0-854C-32C5ECA23FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5169CC30-B6A4-446D-8BBF-39D9C23C43D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{8D8F8A1B-0F64-4D3F-85D3-811D3ECC1CA8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{496416B8-5D2A-421D-BAC1-D85917985C4D}"/>
   </bookViews>
   <sheets>
     <sheet name="15_LTAN06_800km_1213COLD_MY_STT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C6FC404-6231-4306-A719-A70924C7B8DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{629D3D6B-DA3B-40BF-B921-B41131F87713}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
